--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105349_W3.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105349_W3.xlsx
@@ -558,7 +558,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>K. SIMMONS</t>
+          <t>T. LUWAWU-CABARROT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9751</v>
+        <v>2.9547</v>
       </c>
       <c r="E2" t="n">
-        <v>1.53</v>
+        <v>0.2963</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4452</v>
+        <v>2.6584</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4354</v>
+        <v>-0.2676</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7121</v>
+        <v>2.4171</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7233</v>
+        <v>-2.6847</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1943</v>
+        <v>-1.7695</v>
       </c>
       <c r="K2" t="n">
-        <v>1.7094</v>
+        <v>1.0501</v>
       </c>
       <c r="L2" t="n">
-        <v>1.4849</v>
+        <v>-2.8196</v>
       </c>
       <c r="M2" t="n">
-        <v>1.2411</v>
+        <v>1.5019</v>
       </c>
       <c r="N2" t="n">
-        <v>1.0027</v>
+        <v>1.3671</v>
       </c>
       <c r="O2" t="n">
-        <v>0.2384</v>
+        <v>0.1349</v>
       </c>
       <c r="P2" t="n">
-        <v>-1.1538</v>
+        <v>2.0655</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3075</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1538</v>
+        <v>2.0655</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3065</v>
+        <v>-0.7054</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4338</v>
+        <v>-0.2491</v>
       </c>
       <c r="U2" t="n">
-        <v>0.1273</v>
+        <v>-0.4564</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.8623</v>
       </c>
       <c r="W2" t="n">
-        <v>1.077</v>
+        <v>2.3149</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.077</v>
+        <v>-0.4526</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>T. LUWAWU-CABARROT</t>
+          <t>K. SIMMONS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.8935</v>
+        <v>2.9157</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1774</v>
+        <v>1.5172</v>
       </c>
       <c r="F3" t="n">
-        <v>2.716</v>
+        <v>1.3984</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.2744</v>
+        <v>4.3383</v>
       </c>
       <c r="H3" t="n">
-        <v>2.508</v>
+        <v>2.6305</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.7824</v>
+        <v>1.7077</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.9847</v>
+        <v>3.2478</v>
       </c>
       <c r="K3" t="n">
-        <v>1.0035</v>
+        <v>1.7221</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.9881</v>
+        <v>1.5257</v>
       </c>
       <c r="M3" t="n">
-        <v>1.7102</v>
+        <v>1.0904</v>
       </c>
       <c r="N3" t="n">
-        <v>1.5046</v>
+        <v>0.9084</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2057</v>
+        <v>0.182</v>
       </c>
       <c r="P3" t="n">
-        <v>2.0768</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-2.295</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0768</v>
+        <v>1.1475</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.7705</v>
+        <v>-0.2751</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.1381</v>
+        <v>-0.5177</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.6324</v>
+        <v>0.2425</v>
       </c>
       <c r="V3" t="n">
-        <v>1.8615</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2.3002</v>
+        <v>1.082</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4386</v>
+        <v>-1.082</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,64 +736,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8582</v>
+        <v>2.8556</v>
       </c>
       <c r="E4" t="n">
-        <v>1.4765</v>
+        <v>1.5338</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3817</v>
+        <v>1.3218</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0169</v>
+        <v>1.9964</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7813</v>
+        <v>3.7312</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7644</v>
+        <v>-1.7347</v>
       </c>
       <c r="J4" t="n">
-        <v>1.1182</v>
+        <v>1.2823</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4575</v>
+        <v>3.5224</v>
       </c>
       <c r="L4" t="n">
-        <v>-2.3394</v>
+        <v>-2.2401</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8987000000000001</v>
+        <v>0.7141999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3238</v>
+        <v>0.2088</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5749</v>
+        <v>0.5054</v>
       </c>
       <c r="P4" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5432</v>
+        <v>-1.5178</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1801</v>
+        <v>-0.2895</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.363</v>
+        <v>-1.2283</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3428</v>
+        <v>2.3994</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4568</v>
+        <v>0.5589</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8861</v>
+        <v>1.8405</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8626</v>
+        <v>1.8794</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1972</v>
+        <v>-0.1517</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0598</v>
+        <v>2.0311</v>
       </c>
       <c r="J5" t="n">
-        <v>0.6294</v>
+        <v>0.8595</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.8556</v>
+        <v>-0.6663</v>
       </c>
       <c r="L5" t="n">
-        <v>1.4849</v>
+        <v>1.5257</v>
       </c>
       <c r="M5" t="n">
-        <v>1.2333</v>
+        <v>1.0199</v>
       </c>
       <c r="N5" t="n">
-        <v>0.6583</v>
+        <v>0.5145</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5749</v>
+        <v>0.5054</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2043</v>
+        <v>-1.1553</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0735</v>
+        <v>-0.0613</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.2778</v>
+        <v>-1.094</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3923</v>
+        <v>-0.3901</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2461</v>
+        <v>-0.2393</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1545</v>
+        <v>2.1937</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6357</v>
+        <v>-0.5336</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7902</v>
+        <v>2.7272</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1389</v>
+        <v>0.1596</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3042</v>
+        <v>1.3217</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1652</v>
+        <v>-1.1621</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.603</v>
+        <v>-1.3806</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0312</v>
+        <v>0.1251</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.5719</v>
+        <v>-1.5057</v>
       </c>
       <c r="M6" t="n">
-        <v>1.742</v>
+        <v>1.5402</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3353</v>
+        <v>1.1966</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4066</v>
+        <v>0.3437</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0768</v>
+        <v>2.0655</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5997</v>
+        <v>-0.5724</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2826</v>
+        <v>0.1552</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.8823</v>
+        <v>-0.7276</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6847</v>
+        <v>0.6919</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5108</v>
+        <v>1.5017</v>
       </c>
       <c r="E7" t="n">
-        <v>0.626</v>
+        <v>0.6578000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8848</v>
+        <v>0.8438</v>
       </c>
       <c r="G7" t="n">
-        <v>2.092</v>
+        <v>2.0881</v>
       </c>
       <c r="H7" t="n">
-        <v>0.7955</v>
+        <v>0.8014</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2966</v>
+        <v>1.2867</v>
       </c>
       <c r="J7" t="n">
-        <v>2.1702</v>
+        <v>2.2969</v>
       </c>
       <c r="K7" t="n">
-        <v>1.313</v>
+        <v>1.401</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8572</v>
+        <v>0.8959</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.2088</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5175</v>
+        <v>-0.5997</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4394</v>
+        <v>0.3908</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R7" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9495</v>
+        <v>0.9415</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7633</v>
+        <v>0.6559</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1862</v>
+        <v>0.2856</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,64 +1068,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1793</v>
+        <v>1.1323</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5313</v>
+        <v>0.5013</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6479</v>
+        <v>0.631</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1579</v>
+        <v>0.0834</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2239</v>
+        <v>-0.2569</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3819</v>
+        <v>0.3403</v>
       </c>
       <c r="J8" t="n">
-        <v>0.737</v>
+        <v>0.742</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6262</v>
+        <v>0.6309</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1108</v>
+        <v>0.1112</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5790999999999999</v>
+        <v>-0.6587</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8502</v>
+        <v>-0.8878</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2711</v>
+        <v>0.2291</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8749</v>
+        <v>0.8815</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3402</v>
+        <v>0.2803</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5347</v>
+        <v>0.6011</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7617</v>
+        <v>1.7739</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7617</v>
+        <v>1.7739</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1103</v>
+        <v>-0.1228</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3577</v>
+        <v>-0.3493</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2475</v>
+        <v>0.2265</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9119</v>
+        <v>-0.9298999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9294</v>
+        <v>-1.9438</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0175</v>
+        <v>1.0139</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.3626</v>
+        <v>-0.2919</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7398</v>
+        <v>-0.7060999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3772</v>
+        <v>0.4142</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.5493</v>
+        <v>-0.638</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1896</v>
+        <v>-1.2376</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6403</v>
+        <v>0.5996</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1094</v>
+        <v>0.1187</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0049</v>
+        <v>-0.0574</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1045</v>
+        <v>0.176</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,19 +1234,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1692</v>
+        <v>-0.1705</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1692</v>
+        <v>-0.1705</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1692</v>
+        <v>-0.1705</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1692</v>
+        <v>-0.1705</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1692</v>
+        <v>-0.1705</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1692</v>
+        <v>-0.1705</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.9191</v>
+        <v>-0.867</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5807</v>
+        <v>-2.4746</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6616</v>
+        <v>1.6076</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4498</v>
+        <v>0.4423</v>
       </c>
       <c r="H11" t="n">
-        <v>0.2161</v>
+        <v>0.1864</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2337</v>
+        <v>0.2559</v>
       </c>
       <c r="J11" t="n">
-        <v>0.2291</v>
+        <v>0.419</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9068000000000001</v>
+        <v>0.9918</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6777</v>
+        <v>-0.5728</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2207</v>
+        <v>0.0233</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6907</v>
+        <v>-0.8054</v>
       </c>
       <c r="O11" t="n">
-        <v>0.9114</v>
+        <v>0.8288</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4613</v>
+        <v>-3.4424</v>
       </c>
       <c r="R11" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2921</v>
+        <v>-0.2438</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1131</v>
+        <v>0.0078</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4052</v>
+        <v>-0.2517</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W11" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0136</v>
+        <v>-1.0328</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0479</v>
+        <v>0.0489</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0616</v>
+        <v>-1.0816</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2114</v>
+        <v>-1.2113</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2156</v>
+        <v>-1.2012</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0042</v>
+        <v>-0.0101</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4998</v>
+        <v>-0.4645</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5367</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7117</v>
+        <v>-0.7468</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6788999999999999</v>
+        <v>-0.6996</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0327</v>
+        <v>-0.0471</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4615</v>
+        <v>0.459</v>
       </c>
       <c r="S12" t="n">
-        <v>0.667</v>
+        <v>0.6506999999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4015</v>
+        <v>0.3625</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2656</v>
+        <v>0.2882</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9308</v>
+        <v>-0.9312</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.702</v>
+        <v>13.76</v>
       </c>
       <c r="E13" t="n">
-        <v>1.2718</v>
+        <v>1.7567</v>
       </c>
       <c r="F13" t="n">
-        <v>12.4302</v>
+        <v>12.0031</v>
       </c>
       <c r="G13" t="n">
-        <v>8.586600000000001</v>
+        <v>8.408199999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>7.581900000000001</v>
+        <v>7.3642</v>
       </c>
       <c r="I13" t="n">
-        <v>1.005</v>
+        <v>1.044</v>
       </c>
       <c r="J13" t="n">
-        <v>3.6281</v>
+        <v>4.940999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>6.853100000000001</v>
+        <v>7.5695</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2252</v>
+        <v>-2.6284</v>
       </c>
       <c r="M13" t="n">
-        <v>4.958499999999999</v>
+        <v>3.4671</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7285999999999998</v>
+        <v>-0.2051999999999997</v>
       </c>
       <c r="O13" t="n">
-        <v>4.23</v>
+        <v>3.6726</v>
       </c>
       <c r="P13" t="n">
-        <v>3.461300000000001</v>
+        <v>3.442500000000001</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.3838</v>
+        <v>-10.3274</v>
       </c>
       <c r="R13" t="n">
-        <v>13.8453</v>
+        <v>13.77</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.1155</v>
+        <v>-1.8774</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2271</v>
+        <v>0.2867000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-3.3424</v>
+        <v>-2.1646</v>
       </c>
       <c r="V13" t="n">
-        <v>3.7694</v>
+        <v>3.787000000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>6.8007</v>
+        <v>6.856300000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.0312</v>
+        <v>-3.0693</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.611</v>
+        <v>1.6212</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9694</v>
+        <v>1.0095</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6417</v>
+        <v>0.6117</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3355</v>
+        <v>0.3987</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.4906</v>
+        <v>-1.3765</v>
       </c>
       <c r="I14" t="n">
-        <v>1.8261</v>
+        <v>1.7752</v>
       </c>
       <c r="J14" t="n">
-        <v>0.2445</v>
+        <v>0.4371</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.974</v>
+        <v>-0.7856</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2185</v>
+        <v>1.2227</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0911</v>
+        <v>-0.0383</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5165999999999999</v>
+        <v>-0.5908</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6076</v>
+        <v>0.5525</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4615</v>
+        <v>-0.459</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9602</v>
+        <v>2.9143</v>
       </c>
       <c r="T14" t="n">
-        <v>1.8787</v>
+        <v>1.7199</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0815</v>
+        <v>1.1944</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2232</v>
+        <v>-1.2329</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0846</v>
+        <v>1.0711</v>
       </c>
       <c r="E15" t="n">
-        <v>0.8862</v>
+        <v>0.907</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1985</v>
+        <v>0.1641</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6868</v>
+        <v>1.6827</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3495</v>
+        <v>0.3052</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3372</v>
+        <v>1.3775</v>
       </c>
       <c r="J15" t="n">
-        <v>2.0975</v>
+        <v>2.1797</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8632</v>
+        <v>0.8696</v>
       </c>
       <c r="L15" t="n">
-        <v>1.2344</v>
+        <v>1.3101</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.4108</v>
+        <v>-0.497</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5135999999999999</v>
+        <v>-0.5644</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1028</v>
+        <v>0.0674</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.923</v>
+        <v>-0.918</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3209</v>
+        <v>0.3064</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0576</v>
+        <v>-0.1252</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3785</v>
+        <v>0.4316</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1704</v>
+        <v>-0.0265</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7022</v>
+        <v>0.6619</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1882</v>
+        <v>-0.0959</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2892</v>
+        <v>1.3223</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4775</v>
+        <v>-1.4182</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4119</v>
+        <v>-0.1457</v>
       </c>
       <c r="K16" t="n">
-        <v>1.8087</v>
+        <v>1.9396</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.2206</v>
+        <v>-2.0852</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2237</v>
+        <v>0.0498</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5195</v>
+        <v>-0.6173</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7432</v>
+        <v>0.6671</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.923</v>
+        <v>-0.918</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5661</v>
+        <v>0.5672</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7874</v>
+        <v>0.6402</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2213</v>
+        <v>-0.073</v>
       </c>
       <c r="V16" t="n">
-        <v>1.077</v>
+        <v>1.082</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7617</v>
+        <v>1.7739</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4844</v>
+        <v>-0.5258</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1547</v>
+        <v>-2.1554</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6703</v>
+        <v>1.6296</v>
       </c>
       <c r="G17" t="n">
-        <v>0.103</v>
+        <v>0.098</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3275</v>
+        <v>-0.3768</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4305</v>
+        <v>0.4748</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.3543</v>
+        <v>-0.2077</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3603</v>
+        <v>0.4021</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.7147</v>
+        <v>-0.6099</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4574</v>
+        <v>0.3057</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6878</v>
+        <v>-0.779</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1451</v>
+        <v>1.0847</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.3845</v>
+        <v>-1.377</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R17" t="n">
-        <v>0.923</v>
+        <v>0.918</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5817</v>
+        <v>1.5334</v>
       </c>
       <c r="T17" t="n">
-        <v>1.1455</v>
+        <v>0.9767</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4361</v>
+        <v>0.5568</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7846</v>
+        <v>-0.7803</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6384</v>
+        <v>-0.6294</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1462</v>
+        <v>-0.1509</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9229000000000001</v>
+        <v>-0.9526</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2738</v>
+        <v>-1.2223</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3509</v>
+        <v>0.2697</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1052</v>
+        <v>-1.0971</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.0101</v>
+        <v>0.0447</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.0951</v>
+        <v>-1.1417</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.5537</v>
+        <v>-0.3235</v>
       </c>
       <c r="K18" t="n">
-        <v>1.0182</v>
+        <v>1.1823</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5719</v>
+        <v>-1.5057</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.5515</v>
+        <v>-0.7736</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.0282</v>
+        <v>-1.1376</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4768</v>
+        <v>0.364</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R18" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1177</v>
+        <v>-0.1539</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2875</v>
+        <v>0.0978</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4052</v>
+        <v>-0.2517</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3923</v>
+        <v>-0.3901</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1462</v>
+        <v>0.1509</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,64 +1977,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6071</v>
+        <v>-1.6227</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2673</v>
+        <v>-1.2397</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3399</v>
+        <v>-0.3829</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8103</v>
+        <v>-1.8259</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9216</v>
+        <v>-1.8732</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1112</v>
+        <v>0.0473</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.9946</v>
+        <v>-0.8849</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.0685</v>
+        <v>-0.959</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8157</v>
+        <v>-0.9409999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8531</v>
+        <v>-0.9142</v>
       </c>
       <c r="O19" t="n">
-        <v>0.0374</v>
+        <v>-0.0268</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1538</v>
+        <v>1.1475</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4891</v>
+        <v>-1.4852</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8111</v>
+        <v>-0.8958</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5894</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5385</v>
+        <v>0.541</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6525</v>
+        <v>-1.6904</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8543</v>
+        <v>-1.8401</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2018</v>
+        <v>0.1497</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2533</v>
+        <v>-1.2656</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1334</v>
+        <v>0.1188</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3868</v>
+        <v>-1.3844</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.7356</v>
+        <v>-0.5479000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1607</v>
+        <v>1.2476</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.8963</v>
+        <v>-1.7955</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5178</v>
+        <v>-0.7177</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0272</v>
+        <v>-1.1288</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5095</v>
+        <v>0.4111</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R20" t="n">
-        <v>1.846</v>
+        <v>1.836</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0144</v>
+        <v>-0.0313</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0351</v>
+        <v>-0.1447</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0495</v>
+        <v>0.1134</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.077</v>
+        <v>-1.082</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0661</v>
+        <v>-1.9866</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9604</v>
+        <v>-0.8673</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1056</v>
+        <v>-1.1193</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.2311</v>
+        <v>-2.1384</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.8097</v>
+        <v>-2.6976</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5786</v>
+        <v>0.5592</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.7329</v>
+        <v>-2.597</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.8068</v>
+        <v>-2.6711</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0738</v>
+        <v>0.0741</v>
       </c>
       <c r="M21" t="n">
-        <v>0.5019</v>
+        <v>0.4586</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0029</v>
+        <v>-0.0264</v>
       </c>
       <c r="O21" t="n">
-        <v>0.5048</v>
+        <v>0.4851</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="S21" t="n">
-        <v>0.619</v>
+        <v>0.6142</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5493</v>
+        <v>0.4968</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0697</v>
+        <v>0.1174</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2232</v>
+        <v>1.2329</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9079</v>
+        <v>-1.9248</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0772</v>
+        <v>-2.0842</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0999</v>
+        <v>-1.0934</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9772999999999999</v>
+        <v>-0.9908</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2856</v>
+        <v>-0.2957</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3225</v>
+        <v>-0.3328</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0538</v>
+        <v>0.0541</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0169</v>
+        <v>0.0171</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0369</v>
+        <v>0.0371</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3395</v>
+        <v>-0.3498</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3395</v>
+        <v>-0.3498</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0469</v>
+        <v>0.0509</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0469</v>
+        <v>0.0509</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6847</v>
+        <v>-0.6919</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4572</v>
+        <v>-2.4576</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3201</v>
+        <v>-2.3072</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1371</v>
+        <v>-0.1504</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2878</v>
+        <v>-0.2932</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5953000000000001</v>
+        <v>-0.6232</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3075</v>
+        <v>0.33</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4249</v>
+        <v>0.4624</v>
       </c>
       <c r="K23" t="n">
-        <v>0.08459999999999999</v>
+        <v>0.0853</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3403</v>
+        <v>0.3772</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7126</v>
+        <v>-0.7556</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.6798999999999999</v>
+        <v>-0.7085</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0327</v>
+        <v>-0.0471</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6153</v>
+        <v>-1.6065</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.3075</v>
+        <v>-2.295</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6923</v>
+        <v>0.6885</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0156</v>
+        <v>-0.017</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4374</v>
+        <v>-0.4746</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4218</v>
+        <v>0.4577</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.5385</v>
+        <v>-0.541</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,58 +2392,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.5708</v>
+        <v>-3.6033</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1848</v>
+        <v>-3.1678</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.3861</v>
+        <v>-0.4355</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5504</v>
+        <v>-3.5759</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.8767</v>
+        <v>-1.875</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.6738</v>
+        <v>-1.7009</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.9962</v>
+        <v>-1.8938</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1918</v>
+        <v>-1.1224</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.8044</v>
+        <v>-0.7714</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5542</v>
+        <v>-1.682</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6848</v>
+        <v>-0.7524999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8694</v>
+        <v>-0.9295</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2308</v>
+        <v>0.2295</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1538</v>
+        <v>-1.1475</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3845</v>
+        <v>1.377</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2512</v>
+        <v>-0.2569</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0347</v>
+        <v>-0.1265</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2164</v>
+        <v>-0.1304</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.6108</v>
+        <v>-11.5955</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.4301</v>
+        <v>-12.0032</v>
       </c>
       <c r="F25" t="n">
-        <v>0.8194</v>
+        <v>0.4078000000000004</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.586599999999999</v>
+        <v>-8.408300000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.581899999999999</v>
+        <v>-7.3641</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0052</v>
+        <v>-1.0441</v>
       </c>
       <c r="J25" t="n">
-        <v>-4.9585</v>
+        <v>-3.4672</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.7284999999999996</v>
+        <v>0.2054999999999996</v>
       </c>
       <c r="L25" t="n">
-        <v>-4.2302</v>
+        <v>-3.6724</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.628</v>
+        <v>-4.940900000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-6.8531</v>
+        <v>-7.5693</v>
       </c>
       <c r="O25" t="n">
-        <v>3.2251</v>
+        <v>2.6285</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.461100000000001</v>
+        <v>-3.4425</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.8453</v>
+        <v>-13.77</v>
       </c>
       <c r="R25" t="n">
-        <v>10.384</v>
+        <v>10.3275</v>
       </c>
       <c r="S25" t="n">
-        <v>4.2068</v>
+        <v>4.0421</v>
       </c>
       <c r="T25" t="n">
-        <v>3.3427</v>
+        <v>2.1646</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8641999999999997</v>
+        <v>1.8777</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.7695</v>
+        <v>-3.7871</v>
       </c>
       <c r="W25" t="n">
-        <v>3.0312</v>
+        <v>3.0693</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.8007</v>
+        <v>-6.856400000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>

--- a/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105349_W3.xlsx
+++ b/informes_data/ACB/2025-26/playoffs/individual/NP_play_by_play_105349_W3.xlsx
@@ -570,67 +570,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.9547</v>
+        <v>3.0134</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2963</v>
+        <v>0.1148</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6584</v>
+        <v>2.8986</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.2676</v>
+        <v>-0.2683</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4171</v>
+        <v>2.411</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.6847</v>
+        <v>-2.6793</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.7695</v>
+        <v>-1.8286</v>
       </c>
       <c r="K2" t="n">
-        <v>1.0501</v>
+        <v>1.002</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.8196</v>
+        <v>-2.8306</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5019</v>
+        <v>1.5602</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3671</v>
+        <v>1.409</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1349</v>
+        <v>0.1513</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7054</v>
+        <v>-0.6837</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2491</v>
+        <v>-0.3192</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4564</v>
+        <v>-0.3645</v>
       </c>
       <c r="V2" t="n">
-        <v>1.8623</v>
+        <v>1.8596</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3149</v>
+        <v>2.2625</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.4526</v>
+        <v>-0.4029</v>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
@@ -653,67 +653,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.9157</v>
+        <v>2.8742</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5172</v>
+        <v>1.3214</v>
       </c>
       <c r="F3" t="n">
-        <v>1.3984</v>
+        <v>1.5528</v>
       </c>
       <c r="G3" t="n">
-        <v>4.3383</v>
+        <v>4.3072</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6305</v>
+        <v>2.6147</v>
       </c>
       <c r="I3" t="n">
-        <v>1.7077</v>
+        <v>1.6925</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2478</v>
+        <v>3.1752</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7221</v>
+        <v>1.6769</v>
       </c>
       <c r="L3" t="n">
-        <v>1.5257</v>
+        <v>1.4983</v>
       </c>
       <c r="M3" t="n">
-        <v>1.0904</v>
+        <v>1.132</v>
       </c>
       <c r="N3" t="n">
-        <v>0.9084</v>
+        <v>0.9378</v>
       </c>
       <c r="O3" t="n">
-        <v>0.182</v>
+        <v>0.1942</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.2751</v>
+        <v>-0.2631</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5177</v>
+        <v>-0.5782</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2425</v>
+        <v>0.315</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -736,64 +736,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.8556</v>
+        <v>2.8177</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5338</v>
+        <v>1.3418</v>
       </c>
       <c r="F4" t="n">
-        <v>1.3218</v>
+        <v>1.4759</v>
       </c>
       <c r="G4" t="n">
-        <v>1.9964</v>
+        <v>1.9514</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7312</v>
+        <v>3.6741</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.7347</v>
+        <v>-1.7228</v>
       </c>
       <c r="J4" t="n">
-        <v>1.2823</v>
+        <v>1.1693</v>
       </c>
       <c r="K4" t="n">
-        <v>3.5224</v>
+        <v>3.4094</v>
       </c>
       <c r="L4" t="n">
         <v>-2.2401</v>
       </c>
       <c r="M4" t="n">
-        <v>0.7141999999999999</v>
+        <v>0.782</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2088</v>
+        <v>0.2647</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5054</v>
+        <v>0.5173</v>
       </c>
       <c r="P4" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5178</v>
+        <v>-1.5375</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2895</v>
+        <v>-0.3596</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.2283</v>
+        <v>-1.1779</v>
       </c>
       <c r="V4" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W4" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -819,67 +819,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3994</v>
+        <v>2.3982</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5589</v>
+        <v>0.3427</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8405</v>
+        <v>2.0555</v>
       </c>
       <c r="G5" t="n">
-        <v>1.8794</v>
+        <v>1.8433</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1517</v>
+        <v>-0.1723</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0311</v>
+        <v>2.0156</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8595</v>
+        <v>0.7472</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.6663</v>
+        <v>-0.7511</v>
       </c>
       <c r="L5" t="n">
-        <v>1.5257</v>
+        <v>1.4983</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0199</v>
+        <v>1.0961</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5145</v>
+        <v>0.5788</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5054</v>
+        <v>0.5173</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.1553</v>
+        <v>-1.153</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0613</v>
+        <v>-0.141</v>
       </c>
       <c r="U5" t="n">
-        <v>-1.094</v>
+        <v>-1.0121</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.3901</v>
+        <v>-0.3978</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.2393</v>
+        <v>-0.2634</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -902,67 +902,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.1937</v>
+        <v>2.2013</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5336</v>
+        <v>-0.7146</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7272</v>
+        <v>2.9159</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1596</v>
+        <v>0.1331</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3217</v>
+        <v>1.2829</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1621</v>
+        <v>-1.1498</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.3806</v>
+        <v>-1.4656</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1251</v>
+        <v>0.04</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.5057</v>
+        <v>-1.5056</v>
       </c>
       <c r="M6" t="n">
-        <v>1.5402</v>
+        <v>1.5987</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1966</v>
+        <v>1.2429</v>
       </c>
       <c r="O6" t="n">
-        <v>0.3437</v>
+        <v>0.3558</v>
       </c>
       <c r="P6" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>2.0655</v>
+        <v>2.1057</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5724</v>
+        <v>-0.5696</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1552</v>
+        <v>0.0847</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7276</v>
+        <v>-0.6542</v>
       </c>
       <c r="V6" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6919</v>
+        <v>0.6664</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -985,67 +985,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.5017</v>
+        <v>1.4751</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6578000000000001</v>
+        <v>0.468</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8438</v>
+        <v>1.0071</v>
       </c>
       <c r="G7" t="n">
-        <v>2.0881</v>
+        <v>2.0551</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8014</v>
+        <v>0.7803</v>
       </c>
       <c r="I7" t="n">
-        <v>1.2867</v>
+        <v>1.2748</v>
       </c>
       <c r="J7" t="n">
-        <v>2.2969</v>
+        <v>2.1993</v>
       </c>
       <c r="K7" t="n">
-        <v>1.401</v>
+        <v>1.3233</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8959</v>
+        <v>0.876</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2088</v>
+        <v>-0.1443</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5997</v>
+        <v>-0.543</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3908</v>
+        <v>0.3987</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R7" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9415</v>
+        <v>0.9582000000000001</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6559</v>
+        <v>0.6084000000000001</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2856</v>
+        <v>0.3498</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1068,64 +1068,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1323</v>
+        <v>1.1111</v>
       </c>
       <c r="E8" t="n">
-        <v>0.5013</v>
+        <v>0.3668</v>
       </c>
       <c r="F8" t="n">
-        <v>0.631</v>
+        <v>0.7443</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0834</v>
+        <v>0.1132</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2569</v>
+        <v>-0.2338</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3403</v>
+        <v>0.347</v>
       </c>
       <c r="J8" t="n">
-        <v>0.742</v>
+        <v>0.7241</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6309</v>
+        <v>0.6143</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1112</v>
+        <v>0.1098</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6587</v>
+        <v>-0.6109</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.8878</v>
+        <v>-0.8481</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2291</v>
+        <v>0.2372</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S8" t="n">
-        <v>0.8815</v>
+        <v>0.9053</v>
       </c>
       <c r="T8" t="n">
-        <v>0.2803</v>
+        <v>0.2519</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6011</v>
+        <v>0.6533</v>
       </c>
       <c r="V8" t="n">
-        <v>1.7739</v>
+        <v>1.7305</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7739</v>
+        <v>1.7305</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1151,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1228</v>
+        <v>-0.0606</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3493</v>
+        <v>-0.4027</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2265</v>
+        <v>0.3421</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9298999999999999</v>
+        <v>-0.8893</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.9438</v>
+        <v>-1.8927</v>
       </c>
       <c r="I9" t="n">
-        <v>1.0139</v>
+        <v>1.0034</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2919</v>
+        <v>-0.3079</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.7081</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4142</v>
+        <v>0.4002</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.638</v>
+        <v>-0.5814</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2376</v>
+        <v>-1.1846</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5996</v>
+        <v>0.6032</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1187</v>
+        <v>0.1268</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0574</v>
+        <v>-0.0948</v>
       </c>
       <c r="U9" t="n">
-        <v>0.176</v>
+        <v>0.2216</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1234,19 +1234,19 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1261,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1705</v>
+        <v>-0.166</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1317,64 +1317,64 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.867</v>
+        <v>-0.8818</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.4746</v>
+        <v>-2.6988</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6076</v>
+        <v>1.817</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4423</v>
+        <v>0.4453</v>
       </c>
       <c r="H11" t="n">
-        <v>0.1864</v>
+        <v>0.1979</v>
       </c>
       <c r="I11" t="n">
-        <v>0.2559</v>
+        <v>0.2474</v>
       </c>
       <c r="J11" t="n">
-        <v>0.419</v>
+        <v>0.3319</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9918</v>
+        <v>0.9248</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5728</v>
+        <v>-0.5929</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0233</v>
+        <v>0.1134</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8054</v>
+        <v>-0.727</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8288</v>
+        <v>0.8404</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.4424</v>
+        <v>-3.5096</v>
       </c>
       <c r="R11" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2438</v>
+        <v>-0.2213</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0078</v>
+        <v>-0.0532</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2517</v>
+        <v>-0.1682</v>
       </c>
       <c r="V11" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W11" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X11" t="n">
         <v>0</v>
@@ -1400,67 +1400,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.0328</v>
+        <v>-0.9942</v>
       </c>
       <c r="E12" t="n">
-        <v>0.0489</v>
+        <v>0.0101</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0816</v>
+        <v>-1.0044</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.2113</v>
+        <v>-1.1883</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.2012</v>
+        <v>-1.1819</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0101</v>
+        <v>-0.0063</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.4645</v>
+        <v>-0.4722</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.5014999999999999</v>
+        <v>-0.5088</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7468</v>
+        <v>-0.716</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6996</v>
+        <v>-0.6731</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0471</v>
+        <v>-0.043</v>
       </c>
       <c r="P12" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0.459</v>
+        <v>0.4679</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6506999999999999</v>
+        <v>0.6559</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3625</v>
+        <v>0.3481</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2882</v>
+        <v>0.3078</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.9312</v>
+        <v>-0.9298</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1483,67 +1483,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>13.76</v>
+        <v>13.7884</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7567</v>
+        <v>0.1495000000000006</v>
       </c>
       <c r="F13" t="n">
-        <v>12.0031</v>
+        <v>13.6388</v>
       </c>
       <c r="G13" t="n">
-        <v>8.408199999999999</v>
+        <v>8.336699999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>7.3642</v>
+        <v>7.3142</v>
       </c>
       <c r="I13" t="n">
-        <v>1.044</v>
+        <v>1.0225</v>
       </c>
       <c r="J13" t="n">
-        <v>4.940999999999999</v>
+        <v>4.272699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5695</v>
+        <v>7.0227</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6284</v>
+        <v>-2.75</v>
       </c>
       <c r="M13" t="n">
-        <v>3.4671</v>
+        <v>4.0638</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2051999999999997</v>
+        <v>0.2913999999999995</v>
       </c>
       <c r="O13" t="n">
-        <v>3.6726</v>
+        <v>3.7724</v>
       </c>
       <c r="P13" t="n">
-        <v>3.442500000000001</v>
+        <v>3.5094</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.3274</v>
+        <v>-10.5287</v>
       </c>
       <c r="R13" t="n">
-        <v>13.77</v>
+        <v>14.0382</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.8774</v>
+        <v>-1.782</v>
       </c>
       <c r="T13" t="n">
-        <v>0.2867000000000001</v>
+        <v>-0.2528999999999998</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.1646</v>
+        <v>-1.5294</v>
       </c>
       <c r="V13" t="n">
-        <v>3.787000000000001</v>
+        <v>3.724499999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.856300000000001</v>
+        <v>6.6586</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.0693</v>
+        <v>-2.934</v>
       </c>
       <c r="Y13" t="inlineStr"/>
     </row>
@@ -1562,67 +1562,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6212</v>
+        <v>1.6498</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0095</v>
+        <v>0.8374</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6117</v>
+        <v>0.8124</v>
       </c>
       <c r="G14" t="n">
-        <v>0.3987</v>
+        <v>0.3623</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.3765</v>
+        <v>-1.4058</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7752</v>
+        <v>1.7681</v>
       </c>
       <c r="J14" t="n">
-        <v>0.4371</v>
+        <v>0.3406</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7856</v>
+        <v>-0.8673</v>
       </c>
       <c r="L14" t="n">
-        <v>1.2227</v>
+        <v>1.2079</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.0383</v>
+        <v>0.0218</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5908</v>
+        <v>-0.5385</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5525</v>
+        <v>0.5603</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.459</v>
+        <v>-0.4679</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S14" t="n">
-        <v>2.9143</v>
+        <v>2.9538</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7199</v>
+        <v>1.6667</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1944</v>
+        <v>1.2871</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2329</v>
+        <v>-1.1984</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1645,58 +1645,58 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0711</v>
+        <v>1.0427</v>
       </c>
       <c r="E15" t="n">
-        <v>0.907</v>
+        <v>0.7858000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>0.1641</v>
+        <v>0.2568</v>
       </c>
       <c r="G15" t="n">
-        <v>1.6827</v>
+        <v>1.6736</v>
       </c>
       <c r="H15" t="n">
-        <v>0.3052</v>
+        <v>0.3217</v>
       </c>
       <c r="I15" t="n">
-        <v>1.3775</v>
+        <v>1.3519</v>
       </c>
       <c r="J15" t="n">
-        <v>2.1797</v>
+        <v>2.123</v>
       </c>
       <c r="K15" t="n">
-        <v>0.8696</v>
+        <v>0.8467</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3101</v>
+        <v>1.2762</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.497</v>
+        <v>-0.4494</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.5644</v>
+        <v>-0.525</v>
       </c>
       <c r="O15" t="n">
-        <v>0.0674</v>
+        <v>0.0756</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R15" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3064</v>
+        <v>0.305</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1252</v>
+        <v>-0.1673</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4316</v>
+        <v>0.4723</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1728,67 +1728,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6354</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0265</v>
+        <v>-0.3088</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6619</v>
+        <v>0.8758</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0959</v>
+        <v>-0.142</v>
       </c>
       <c r="H16" t="n">
-        <v>1.3223</v>
+        <v>1.2753</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.4182</v>
+        <v>-1.4172</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1457</v>
+        <v>-0.2689</v>
       </c>
       <c r="K16" t="n">
-        <v>1.9396</v>
+        <v>1.8272</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.0852</v>
+        <v>-2.0961</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0498</v>
+        <v>0.1269</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6173</v>
+        <v>-0.552</v>
       </c>
       <c r="O16" t="n">
-        <v>0.6671</v>
+        <v>0.6788</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.918</v>
+        <v>-0.9359</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R16" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5672</v>
+        <v>0.5808</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6402</v>
+        <v>0.5693</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.073</v>
+        <v>0.0115</v>
       </c>
       <c r="V16" t="n">
-        <v>1.082</v>
+        <v>1.0641</v>
       </c>
       <c r="W16" t="n">
-        <v>1.7739</v>
+        <v>1.7305</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1811,67 +1811,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.5258</v>
+        <v>-0.5432</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.1554</v>
+        <v>-2.3587</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6296</v>
+        <v>1.8154</v>
       </c>
       <c r="G17" t="n">
-        <v>0.098</v>
+        <v>0.1159</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.3768</v>
+        <v>-0.3424</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4748</v>
+        <v>0.4583</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.2077</v>
+        <v>-0.2584</v>
       </c>
       <c r="K17" t="n">
-        <v>0.4021</v>
+        <v>0.3711</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6099</v>
+        <v>-0.6294999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3057</v>
+        <v>0.3743</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.779</v>
+        <v>-0.7135</v>
       </c>
       <c r="O17" t="n">
-        <v>1.0847</v>
+        <v>1.0878</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.377</v>
+        <v>-1.4038</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R17" t="n">
-        <v>0.918</v>
+        <v>0.9359</v>
       </c>
       <c r="S17" t="n">
-        <v>1.5334</v>
+        <v>1.5402</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9767</v>
+        <v>0.9006999999999999</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5568</v>
+        <v>0.6395</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7803</v>
+        <v>-0.7955</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.6294</v>
+        <v>-0.6612</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1509</v>
+        <v>-0.1343</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
@@ -1894,67 +1894,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.9526</v>
+        <v>-0.9765</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2223</v>
+        <v>-1.482</v>
       </c>
       <c r="F18" t="n">
-        <v>0.2697</v>
+        <v>0.5054999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0971</v>
+        <v>-1.1023</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0447</v>
+        <v>0.0148</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1417</v>
+        <v>-1.1171</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3235</v>
+        <v>-0.4362</v>
       </c>
       <c r="K18" t="n">
-        <v>1.1823</v>
+        <v>1.0693</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.5057</v>
+        <v>-1.5056</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.7736</v>
+        <v>-0.6661</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.1376</v>
+        <v>-1.0545</v>
       </c>
       <c r="O18" t="n">
-        <v>0.364</v>
+        <v>0.3885</v>
       </c>
       <c r="P18" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R18" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1539</v>
+        <v>-0.1784</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0978</v>
+        <v>-0.0102</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2517</v>
+        <v>-0.1682</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3901</v>
+        <v>-0.3978</v>
       </c>
       <c r="W18" t="n">
-        <v>0.1509</v>
+        <v>0.1343</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
@@ -1977,64 +1977,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6227</v>
+        <v>-1.6086</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.2397</v>
+        <v>-1.3553</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3829</v>
+        <v>-0.2533</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.8259</v>
+        <v>-1.7939</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8732</v>
+        <v>-1.8568</v>
       </c>
       <c r="I19" t="n">
-        <v>0.0473</v>
+        <v>0.0629</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.8849</v>
+        <v>-0.922</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.959</v>
+        <v>-0.9952</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9409999999999999</v>
+        <v>-0.8718</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9142</v>
+        <v>-0.8616</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0268</v>
+        <v>-0.0103</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1475</v>
+        <v>1.1699</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4852</v>
+        <v>-1.5167</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8958</v>
+        <v>-0.9653</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5894</v>
+        <v>-0.5513</v>
       </c>
       <c r="V19" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="W19" t="n">
-        <v>0.541</v>
+        <v>0.5321</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -2060,67 +2060,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6904</v>
+        <v>-1.6496</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8401</v>
+        <v>-2.0493</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1497</v>
+        <v>0.3997</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.2656</v>
+        <v>-1.2456</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1188</v>
+        <v>0.1238</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3844</v>
+        <v>-1.3694</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.5479000000000001</v>
+        <v>-0.627</v>
       </c>
       <c r="K20" t="n">
-        <v>1.2476</v>
+        <v>1.1739</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.7955</v>
+        <v>-1.8008</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.7177</v>
+        <v>-0.6186</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1288</v>
+        <v>-1.05</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4111</v>
+        <v>0.4314</v>
       </c>
       <c r="P20" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R20" t="n">
-        <v>1.836</v>
+        <v>1.8718</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0313</v>
+        <v>-0.0418</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1447</v>
+        <v>-0.2525</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1134</v>
+        <v>0.2107</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.082</v>
+        <v>-1.0641</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
@@ -2143,67 +2143,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9866</v>
+        <v>-1.9456</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8673</v>
+        <v>-0.9337</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1193</v>
+        <v>-1.0119</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1384</v>
+        <v>-2.1385</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.6976</v>
+        <v>-2.6964</v>
       </c>
       <c r="I21" t="n">
-        <v>0.5592</v>
+        <v>0.5578</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.597</v>
+        <v>-2.6097</v>
       </c>
       <c r="K21" t="n">
-        <v>-2.6711</v>
+        <v>-2.6829</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0741</v>
+        <v>0.0732</v>
       </c>
       <c r="M21" t="n">
-        <v>0.4586</v>
+        <v>0.4711</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0264</v>
+        <v>-0.0135</v>
       </c>
       <c r="O21" t="n">
-        <v>0.4851</v>
+        <v>0.4846</v>
       </c>
       <c r="P21" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6142</v>
+        <v>0.6253</v>
       </c>
       <c r="T21" t="n">
-        <v>0.4968</v>
+        <v>0.4776</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1174</v>
+        <v>0.1477</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="W21" t="n">
-        <v>1.2329</v>
+        <v>1.1984</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9248</v>
+        <v>-1.8648</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2226,67 +2226,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0842</v>
+        <v>-2.0652</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.0934</v>
+        <v>-1.1167</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.9908</v>
+        <v>-0.9486</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.2957</v>
+        <v>-0.2833</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3328</v>
+        <v>-0.3199</v>
       </c>
       <c r="I22" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0541</v>
+        <v>0.0532</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0171</v>
+        <v>0.0166</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0371</v>
+        <v>0.0366</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.3498</v>
+        <v>-0.3365</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3498</v>
+        <v>-0.3365</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0509</v>
+        <v>0.0543</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0509</v>
+        <v>0.0543</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6919</v>
+        <v>-0.6664</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2309,67 +2309,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.4576</v>
+        <v>-2.4619</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.3072</v>
+        <v>-2.4001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1504</v>
+        <v>-0.0617</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.2932</v>
+        <v>-0.2739</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.6232</v>
+        <v>-0.5946</v>
       </c>
       <c r="I23" t="n">
-        <v>0.33</v>
+        <v>0.3206</v>
       </c>
       <c r="J23" t="n">
-        <v>0.4624</v>
+        <v>0.4466</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0853</v>
+        <v>0.083</v>
       </c>
       <c r="L23" t="n">
-        <v>0.3772</v>
+        <v>0.3636</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.7556</v>
+        <v>-0.7205</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7085</v>
+        <v>-0.6776</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0471</v>
+        <v>-0.043</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6065</v>
+        <v>-1.6378</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.295</v>
+        <v>-2.3397</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6885</v>
+        <v>0.7019</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.017</v>
+        <v>-0.0181</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.4746</v>
+        <v>-0.507</v>
       </c>
       <c r="U23" t="n">
-        <v>0.4577</v>
+        <v>0.4889</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.541</v>
+        <v>-0.5321</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2392,58 +2392,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.6033</v>
+        <v>-3.5409</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.1678</v>
+        <v>-3.2575</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4355</v>
+        <v>-0.2834</v>
       </c>
       <c r="G24" t="n">
-        <v>-3.5759</v>
+        <v>-3.5089</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.875</v>
+        <v>-1.8339</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.7009</v>
+        <v>-1.6749</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.8938</v>
+        <v>-1.905</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.1224</v>
+        <v>-1.1339</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7714</v>
+        <v>-0.7711</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.682</v>
+        <v>-1.6039</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.7524999999999999</v>
+        <v>-0.7</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.9295</v>
+        <v>-0.9039</v>
       </c>
       <c r="P24" t="n">
-        <v>0.2295</v>
+        <v>0.234</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1475</v>
+        <v>-1.1699</v>
       </c>
       <c r="R24" t="n">
-        <v>1.377</v>
+        <v>1.4038</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.2569</v>
+        <v>-0.266</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.1265</v>
+        <v>-0.1827</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1304</v>
+        <v>-0.0834</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2475,67 +2475,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-11.5955</v>
+        <v>-11.532</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.0032</v>
+        <v>-13.6389</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4078000000000004</v>
+        <v>2.1067</v>
       </c>
       <c r="G25" t="n">
-        <v>-8.408300000000001</v>
+        <v>-8.336600000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>-7.3641</v>
+        <v>-7.314199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.0441</v>
+        <v>-1.0224</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.4672</v>
+        <v>-4.0638</v>
       </c>
       <c r="K25" t="n">
-        <v>0.2054999999999996</v>
+        <v>-0.2915000000000005</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.6724</v>
+        <v>-3.772400000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.940900000000001</v>
+        <v>-4.2727</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.5693</v>
+        <v>-7.0227</v>
       </c>
       <c r="O25" t="n">
-        <v>2.6285</v>
+        <v>2.7498</v>
       </c>
       <c r="P25" t="n">
-        <v>-3.4425</v>
+        <v>-3.5095</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.77</v>
+        <v>-14.0385</v>
       </c>
       <c r="R25" t="n">
-        <v>10.3275</v>
+        <v>10.5288</v>
       </c>
       <c r="S25" t="n">
-        <v>4.0421</v>
+        <v>4.0384</v>
       </c>
       <c r="T25" t="n">
-        <v>2.1646</v>
+        <v>1.5293</v>
       </c>
       <c r="U25" t="n">
-        <v>1.8777</v>
+        <v>2.5091</v>
       </c>
       <c r="V25" t="n">
-        <v>-3.7871</v>
+        <v>-3.7245</v>
       </c>
       <c r="W25" t="n">
-        <v>3.0693</v>
+        <v>2.9341</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.856400000000001</v>
+        <v>-6.658600000000001</v>
       </c>
       <c r="Y25" t="inlineStr"/>
     </row>
